--- a/智能评估.xlsx
+++ b/智能评估.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27860" windowHeight="14860"/>
+    <workbookView windowHeight="14860" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="科技管理应用" sheetId="1" r:id="rId1"/>
+    <sheet name="巡查问题在线管理" sheetId="2" r:id="rId2"/>
+    <sheet name="项目管理应用" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
   <si>
     <t>b级节点</t>
   </si>
@@ -90,6 +92,117 @@
   </si>
   <si>
     <t>{里程碑状态:field}-【执行进度:field】</t>
+  </si>
+  <si>
+    <t>科技成果模块新增一个成果库页面</t>
+  </si>
+  <si>
+    <t>在【科技成果管理:moudle】模块新增一个{成果库:page}页面，页面包含一些查询条件和一个列表，列表是已经审核通过的成果信息，用户选择查询条件，点击{查询:action}按钮，进行成果查询</t>
+  </si>
+  <si>
+    <t>进入科技管理模块，点击成果库页签，会查看已经审核通过的所有成果，用户可以进行筛选，查看成果详情</t>
+  </si>
+  <si>
+    <t>{成果库:page}</t>
+  </si>
+  <si>
+    <t>【科技成果管理:moudle】</t>
+  </si>
+  <si>
+    <t>科技成果管理新增一个页面，审核通过的成果会展示在这个页面里</t>
+  </si>
+  <si>
+    <t>{查询:action}</t>
+  </si>
+  <si>
+    <t>巡查问题在线管理</t>
+  </si>
+  <si>
+    <t>人才基本信息页面新增一个上传简历功能</t>
+  </si>
+  <si>
+    <t>在【人才信息管理:moudle】模块【人才基本信息:page】页面新增一个{上传:action}按钮，用户点击按钮，上传自己的简历后点击【保存:action】按钮后，后续可下载查看详情，仅允许上传PDF格式</t>
+  </si>
+  <si>
+    <t>进入人才信息管理模块，用户可上传简历，便于简历信息的在线管理</t>
+  </si>
+  <si>
+    <t>{上传:action}</t>
+  </si>
+  <si>
+    <t>【人才基本信息:page】</t>
+  </si>
+  <si>
+    <t>增加一个上传按钮</t>
+  </si>
+  <si>
+    <t>【保存:action】</t>
+  </si>
+  <si>
+    <t>需对上传的文件进行保存，后续可从详情中查看</t>
+  </si>
+  <si>
+    <t>{上传:action}-【保存:action】</t>
+  </si>
+  <si>
+    <t>组队选才页面新增角色要求功能</t>
+  </si>
+  <si>
+    <t>在【任务管理:moudle】模块【组队选才:page】页面新增一个{角色要求:field}字段，用户选择相关角色要求，点击【生成初选名单:action】按钮，根据用户选择的要求，生成这个任务的相关的角色</t>
+  </si>
+  <si>
+    <t>进入组队选才页面，可根据选择的要求生成任务的角色，提升了效率</t>
+  </si>
+  <si>
+    <t>{角色要求:field}</t>
+  </si>
+  <si>
+    <t>【组队选才:page】</t>
+  </si>
+  <si>
+    <t>增加一个角色要求字段</t>
+  </si>
+  <si>
+    <t>【生成初选名单:action】</t>
+  </si>
+  <si>
+    <t>生成初选名单后需遵循所选的角色要求，考虑后台逻辑的调整</t>
+  </si>
+  <si>
+    <t>{角色要求:field}-【生成初选名单:action】</t>
+  </si>
+  <si>
+    <t>项目管理应用</t>
+  </si>
+  <si>
+    <t>成员管理里新增一个人员报工功能</t>
+  </si>
+  <si>
+    <t>在【成员管理:page】页面新增一个{人员报工:action}按钮，点击这个按钮出现一个弹窗，用户需要维护{报工日期:field} {报工内容:field}等字段，然后点击{提交:action}按钮进行审核</t>
+  </si>
+  <si>
+    <t>进入成员管理页面，用户点击报工，维护完信息后进行审核，有效的提升了项目工作开展的效率</t>
+  </si>
+  <si>
+    <t>{人员报工:action}</t>
+  </si>
+  <si>
+    <t>【成员管理:page】</t>
+  </si>
+  <si>
+    <t>增加一个报工按钮，需考虑是否进行报工内容展示</t>
+  </si>
+  <si>
+    <t>【成员管理:page】-{人员报工:action}</t>
+  </si>
+  <si>
+    <t>{报工日期:field}</t>
+  </si>
+  <si>
+    <t>{报工内容:field}</t>
+  </si>
+  <si>
+    <t>{提交:action}</t>
   </si>
 </sst>
 </file>
@@ -449,7 +562,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -482,6 +595,17 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -622,7 +746,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -634,34 +758,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -746,7 +870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -765,17 +889,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1302,7 +1429,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="18.1057692307692" customWidth="1"/>
@@ -1345,7 +1472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="118" spans="1:9">
+    <row r="2" ht="51" spans="1:9">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1370,123 +1497,526 @@
       <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:9">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+    <row r="4" ht="51" spans="1:9">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" ht="17" spans="1:9">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="34" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" ht="34" spans="1:9">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="34" spans="1:9">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" ht="51" spans="1:9">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" ht="84" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:9">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" ht="17" spans="1:9">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" ht="17" spans="1:9">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="18.1057692307692" customWidth="1"/>
+    <col min="2" max="2" width="33.9711538461538" customWidth="1"/>
+    <col min="3" max="3" width="39.9038461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.7403846153846" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.6057692307692" style="1" customWidth="1"/>
+    <col min="6" max="7" width="18.1057692307692" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7980769230769" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.0192307692308" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.23076923076923" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="17" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" customFormat="1" ht="34" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" customFormat="1" ht="34" spans="1:10">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" customFormat="1" ht="34" spans="1:10">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" customFormat="1" ht="51" spans="1:10">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="18.1057692307692" customWidth="1"/>
+    <col min="2" max="2" width="33.9711538461538" customWidth="1"/>
+    <col min="3" max="3" width="39.9038461538462" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.7403846153846" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.6057692307692" style="1" customWidth="1"/>
+    <col min="6" max="7" width="18.1057692307692" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7980769230769" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.0192307692308" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.23076923076923" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" ht="17" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" customFormat="1" ht="34" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" customFormat="1" ht="17" spans="1:10">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" customFormat="1" ht="17" spans="1:10">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" customFormat="1" ht="17" spans="1:10">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="J5" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="E2:E5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
